--- a/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="B1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,21 @@
           <t>Y/N</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -1170,6 +1185,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -1192,6 +1218,17 @@
           <t>No</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -1214,6 +1251,17 @@
           <t>TBC</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1225,6 +1273,17 @@
         <is>
           <t>Support meeting</t>
         </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use institutional research output data (e.g. SDG-mapped publications via SciVal) to provide the University-wide quantitative picture of sustainability-related research in the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Nature and biodiversity section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on the baseline nature footprint of the University's supply chain in the Nature and biodiversity section of the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr"/>

--- a/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,32 @@
       <sz val="22"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -80,12 +107,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <color rgb="000E2841"/>
@@ -100,11 +121,9 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
+      <color rgb="000563C1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -116,7 +135,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,17 +155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,12 +166,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin">
@@ -168,62 +181,73 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +623,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="24" customWidth="1" min="11" max="11"/>
@@ -650,7 +674,7 @@
 • Provide commentary on progress towards each target (Column M or N)
 • Provide supporting documentation if required (Column O), including links to images
 • Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
-• Your end-2025 responses (where a related target existed) can be viewed by clicking the [+] icon above Columns H–K
+• Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
 • Due: Friday 15 January 2027 (TBC). Questions: Sustainability Strategy team (sustainability-strategy@unimelb.edu.au – TBC)</t>
@@ -728,7 +752,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -896,7 +920,8 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>currently mapped to the SDGs using SciVal</t>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 5b(iii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+currently mapped to the SDGs using SciVal</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -904,9 +929,22 @@
           <t>We will use institutional research output data (e.g. SDG-mapped publications via SciVal) to provide the University-wide quantitative picture of sustainability-related research in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>5b(iii)
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>The University’s research outputs continue to be extensively mentioned in patents, policy, news and social media.</t>
+        </is>
+      </c>
       <c r="K16" s="19" t="inlineStr"/>
       <c r="L16" s="19" t="n"/>
       <c r="M16" s="19" t="n"/>
@@ -947,7 +985,11 @@
           <t>We will report on the baseline nature footprint of the University's supply chain in the Nature and biodiversity section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr"/>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I17" s="19" t="inlineStr"/>
       <c r="J17" s="19" t="inlineStr"/>
       <c r="K17" s="19" t="inlineStr"/>
@@ -980,6 +1022,9 @@
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" location="'3. SR25 responses'!B10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1030,7 +1075,7 @@
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Friday 4 December 2026 (TBC) (early submission helps us develop case studies).</t>
         </is>
@@ -1038,47 +1083,47 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="22" t="inlineStr"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr"/>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
@@ -1327,4 +1372,383 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2025 target status assessment and reporting (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Your SR25 responses – Melbourne Research and Enterprise (MRE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>← Back to request</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Chancellery Research and Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SR25 ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>SP2030 target</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>2025 reporting request</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed end-2025 status</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 1: Target-level reporting</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 2: Indicator-level reporting</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Supporting information/comments</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Related SR26 indicator(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>The University has curated living labs covering the priority areas of this Plan</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Report on living labs at the University - outputs, outcomes and impact.</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>"We continue to encourage strong sustainability practices within the Portfolio and across the University, and in particular when implementing new Research Strategy: Advancing Research: 2030: Excellence for Impact. 
+Melbourne Connect have achieved remarkable sustainability credentials, earning 6 Star Green Star ratings for both its commercial and student accommodation buildings, as well as for the Faculty of Engineering and Information Technology's interior fit-out. These accolades from the Green Building Council of Australia underscore the University's dedication to world-leading, environmentally-sustainable building practices, setting a benchmark for future developments. "</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>EN1(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="160" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>5a(i)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Sustainability research is integrated with campus operations and planning, to be an international exemplar of a sustainable community</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Narrative detailing the University-wide efforts (such as funding, governance structures, and incentives) that have been established and used to facilitate two-way exchange between researchers and research into campus operations and planning</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>"The Melbourne Biodiversity Institute launched, with academic and professional staff at the University collaborating to enhance biodiversity outcomes on and beyond our campuses. In its first year MBI secured funds alongside local and national partners, and advanced 12 biodiversity projects with real-world outcomes. With partners spanning government, business and finance, energy and sustainability, organisations, research outcomes from the institute inlude assessing whether carbon and biodiversisty markets support First Peoples caring for Country, rapid energy transitions and renewables infrastructure. 
+We are implementing our new Research Strategy 'Advancing Research 2030 - Excellence for Impact' with a key initiative 'Melbourne Impact Accelerators' designed to address the complex challenges we face and deliver lasting impact. A key Impact Accelerator is 'Climate Sustainability and Ecosystem Health'.  The research will help build resilience, support new energy transitions, improve biodiversity, help reverse habitat loss and contribute to effective policy. " Implementation is underway over 2026 and 2027.</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>TR1(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="160" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>5a(ii)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Sustainability research is integrated with campus operations and planning, to be an international exemplar of a sustainable community</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>As for 2a</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>We continue to support and develop Melbourne Climate Futures, a key Centre with a focus on connecting and amplifying the depth and breadth of the University of Melbourne, research, collaboration and empowerment. Several initiatives developed by the Melbourne Climate Futures, such as the carbon footprint calculator, have contributed to stronger reporting on the amount of CO2.</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="160" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>5b(iii)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Percentage of the University's research outputs that map to one or more SDGs in the top 10 per cent most cited in their field; Number of patent, policy and news/social media mentions for University research outputs mapped to SDGs</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>The University’s research outputs continue to be extensively mentioned in patents, policy, news and social media.</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="160" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>5b(ii)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Commentary on use of communication channels to disseminate sustainability-related research, e.g. OnePlanet report</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>The University’s research outputs continue to be extensively mentioned in patents, policy, news and social media. Data is below on University research outputs for 2025 so far.</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>TR2(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="160" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>5b(iv)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Please provide data on the number of researchers across UOM whose research is linked to sustainability. This could be based on information from the SDG Reporting dashboard developed by James Lewis in Enterprise Performance Reporting</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Response from Shane Wood received 2/2/26</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr"/>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>5c(i)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Description of where education on sustainability impacts of research is embedded in researcher induction, including graduate researcher training</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>We continue to encourage all researchers at the University to consider the impacts of their research, including in relation to sustainability through the Research in a Publicly Spirited University, and Openness Transparency agenda in the new Research Strategy.</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>TR3(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="160" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>5c(ii)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Case studies documenting the development and use of various tools, resources and approaches to address the sustainability impacts of research.</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>We continue to hold seminars, with professionals and academics to discuss opportunities to expand our sustainability efforts across the University. Initiatives like the MCF Seminar Series, a series of seminars designed to bring together researchers, practitioners, and the public to discuss various aspects of climate change and sustainability, continues its third year as Melbourne Connect, with Academics and Professionals alike in attendance. Deep-Dive sessions are also held with colleagues to discuss sustainability impacts and initiatives, presented by the Sustainability Team.</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="19" t="inlineStr"/>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>TR3(b)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/MRE - end-2026 sustainability reporting request.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Quantitative data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,7 +48,14 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="000E2841"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -54,13 +64,29 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000E2841"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -97,26 +123,8 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="000E2841"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
       <color rgb="000E2841"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="000E2841"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -135,17 +143,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +163,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,63 +199,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -921,7 +947,8 @@
       <c r="F16" s="19" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 5b(iii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-currently mapped to the SDGs using SciVal</t>
+currently mapped to the SDGs using SciVal
+Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -977,7 +1004,8 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Impact Encore Measurement</t>
+          <t>Impact Encore Measurement
+Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -1169,217 +1197,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>End 2026 target status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data owner confirms</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Request status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Please select from dropdown</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not sent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Partially – see comments</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chased</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Support meeting</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1751,4 +1568,3897 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O111"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2026 target status assessment and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative data – Melbourne Research and Enterprise (MRE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional figures are fine; we will confirm final figures with you in February), the data source, and any change to definition or boundary. Due: Friday 15 January 2027 (TBC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Context only (please do not alter)</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Please fill in these cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>CY2023</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>CY2024</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>CY2025</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Data status</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>CY2026 value</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Data source (file name, link or system)</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>Change to definition or boundary?</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Notes / limitations</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>Useful case studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>No instructions – context only.</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr"/>
+      <c r="D7" s="26" t="inlineStr"/>
+      <c r="E7" s="26" t="inlineStr"/>
+      <c r="F7" s="26" t="inlineStr"/>
+      <c r="G7" s="26" t="inlineStr"/>
+      <c r="H7" s="26" t="inlineStr"/>
+      <c r="I7" s="26" t="inlineStr"/>
+      <c r="J7" s="26" t="inlineStr"/>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>Please enter numerical values</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>Please provide a file name or link to the data source</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>Describe any change since last year (or 'No change')</t>
+        </is>
+      </c>
+      <c r="N7" s="26" t="inlineStr">
+        <is>
+          <t>Please add any additional notes here</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="inlineStr">
+        <is>
+          <t>Please provide information on any useful case studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Documented progress of relevant strategic initiatives, including Impact Accelerators</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Completion rate to the set annual target of strategic initiatives</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="27" t="inlineStr"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>Impact Accelerators</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Strategic Initiatives 2</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="19" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>Strategic Initiatives 3</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="31" t="n"/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Strategic Initiatives on track</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>TR2(b)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Strategic Initiatives delivered</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Expert-reviewed summary of sustainability-related research outputs, outcomes and influence using available institutional evidence sources</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>SDG-related research outputs in the top 10% of citations</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="27" t="inlineStr"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>SDG 1 - No Poverty</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="31" t="n">
+        <v>424</v>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr"/>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>SDG 2 - Zero Hunger</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n">
+        <v>781</v>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="19" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>SDG 3 - Good health and well-being</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n">
+        <v>15195</v>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="19" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr"/>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>SDG 4 - Quality Education</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n">
+        <v>1292</v>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>SDG 5 - Gender Equality</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
+      <c r="I19" s="31" t="n">
+        <v>1275</v>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="19" t="n"/>
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr"/>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>SDG 6 - Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n">
+        <v>661</v>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="n"/>
+      <c r="O20" s="19" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr"/>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>SDG 7 - Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="31" t="n"/>
+      <c r="I21" s="31" t="n">
+        <v>997</v>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr"/>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>SDG 8 - Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n">
+        <v>995</v>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr"/>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>SDG 9 - Industry, innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n">
+        <v>1457</v>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr"/>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>SDG 10 - Reduced inequality</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n">
+        <v>1617</v>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n"/>
+      <c r="N24" s="19" t="n"/>
+      <c r="O24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr"/>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>SDG 11 - Sustainable cities and communities</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n">
+        <v>1436</v>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr"/>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>SDG 12 - Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n">
+        <v>838</v>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="19" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>SDG 13 - Climate action</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="31" t="n"/>
+      <c r="I27" s="31" t="n">
+        <v>1624</v>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr"/>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>SDG 14 - Life below water</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n">
+        <v>442</v>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n"/>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="19" t="n"/>
+      <c r="N28" s="19" t="n"/>
+      <c r="O28" s="19" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr"/>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>SDG 15 - Life on land</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="31" t="n"/>
+      <c r="I29" s="31" t="n">
+        <v>1015</v>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="19" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr"/>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>SDG 16 - Peace, justice and strong institutions</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K30" s="19" t="n"/>
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="19" t="n"/>
+      <c r="N30" s="19" t="n"/>
+      <c r="O30" s="19" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr"/>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>SDG-related research outputs in the top 10% of citations (Field-weighted)</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr"/>
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="28" t="n"/>
+      <c r="J31" s="27" t="inlineStr"/>
+      <c r="K31" s="29" t="n"/>
+      <c r="L31" s="29" t="n"/>
+      <c r="M31" s="29" t="n"/>
+      <c r="N31" s="29" t="n"/>
+      <c r="O31" s="29" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr"/>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>SDG 1 - No Poverty</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n"/>
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n"/>
+      <c r="N32" s="19" t="n"/>
+      <c r="O32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr"/>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>SDG 2 - Zero Hunger</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="31" t="n"/>
+      <c r="I33" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="19" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr"/>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>SDG 3 - Good health and well-being</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n"/>
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="19" t="n"/>
+      <c r="N34" s="19" t="n"/>
+      <c r="O34" s="19" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr"/>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>SDG 4 - Quality Education</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="19" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr"/>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>SDG 5 - Gender Equality</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n"/>
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n"/>
+      <c r="N36" s="19" t="n"/>
+      <c r="O36" s="19" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr"/>
+      <c r="D37" s="30" t="inlineStr">
+        <is>
+          <t>SDG 6 - Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="19" t="n"/>
+      <c r="O37" s="19" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr"/>
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>SDG 7 - Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n"/>
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="19" t="n"/>
+      <c r="N38" s="19" t="n"/>
+      <c r="O38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr"/>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>SDG 8 - Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr"/>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>SDG 9 - Industry, innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="31" t="n"/>
+      <c r="I40" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="n"/>
+      <c r="L40" s="19" t="n"/>
+      <c r="M40" s="19" t="n"/>
+      <c r="N40" s="19" t="n"/>
+      <c r="O40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr"/>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>SDG 10 - Reduced inequality</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="31" t="n"/>
+      <c r="I41" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="n"/>
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="19" t="n"/>
+      <c r="N41" s="19" t="n"/>
+      <c r="O41" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr"/>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>SDG 11 - Sustainable cities and communities</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K42" s="19" t="n"/>
+      <c r="L42" s="19" t="n"/>
+      <c r="M42" s="19" t="n"/>
+      <c r="N42" s="19" t="n"/>
+      <c r="O42" s="19" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr"/>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>SDG 12 - Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="31" t="n"/>
+      <c r="I43" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n"/>
+      <c r="N43" s="19" t="n"/>
+      <c r="O43" s="19" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr"/>
+      <c r="D44" s="30" t="inlineStr">
+        <is>
+          <t>SDG 13 - Climate action</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="31" t="n"/>
+      <c r="I44" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="19" t="n"/>
+      <c r="N44" s="19" t="n"/>
+      <c r="O44" s="19" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr"/>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>SDG 14 - Life below water</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="31" t="n"/>
+      <c r="I45" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n"/>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="19" t="n"/>
+      <c r="N45" s="19" t="n"/>
+      <c r="O45" s="19" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr"/>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>SDG 15 - Life on land</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="n"/>
+      <c r="G46" s="31" t="n"/>
+      <c r="H46" s="31" t="n"/>
+      <c r="I46" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n"/>
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="19" t="n"/>
+      <c r="N46" s="19" t="n"/>
+      <c r="O46" s="19" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr"/>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>SDG 16 - Peace, justice and strong institutions</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="n"/>
+      <c r="G47" s="31" t="n"/>
+      <c r="H47" s="31" t="n"/>
+      <c r="I47" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="n"/>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="19" t="n"/>
+      <c r="N47" s="19" t="n"/>
+      <c r="O47" s="19" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr"/>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>SDG-related research outputs mentioned in Patents</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="31" t="n"/>
+      <c r="I48" s="31" t="n">
+        <v>651</v>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="n"/>
+      <c r="L48" s="19" t="n"/>
+      <c r="M48" s="19" t="n"/>
+      <c r="N48" s="19" t="n"/>
+      <c r="O48" s="19" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr"/>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>SDG 1 - No Poverty</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="n"/>
+      <c r="G49" s="31" t="n"/>
+      <c r="H49" s="31" t="n"/>
+      <c r="I49" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="n"/>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="19" t="n"/>
+      <c r="N49" s="19" t="n"/>
+      <c r="O49" s="19" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr"/>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>SDG 2 - Zero Hunger</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="n"/>
+      <c r="G50" s="31" t="n"/>
+      <c r="H50" s="31" t="n"/>
+      <c r="I50" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K50" s="19" t="n"/>
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="19" t="n"/>
+      <c r="N50" s="19" t="n"/>
+      <c r="O50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr"/>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>SDG 3 - Good health and well-being</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="n"/>
+      <c r="G51" s="31" t="n"/>
+      <c r="H51" s="31" t="n"/>
+      <c r="I51" s="31" t="n">
+        <v>564</v>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="n"/>
+      <c r="L51" s="19" t="n"/>
+      <c r="M51" s="19" t="n"/>
+      <c r="N51" s="19" t="n"/>
+      <c r="O51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr"/>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>SDG 4 - Quality Education</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="n"/>
+      <c r="G52" s="31" t="n"/>
+      <c r="H52" s="31" t="n"/>
+      <c r="I52" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="n"/>
+      <c r="L52" s="19" t="n"/>
+      <c r="M52" s="19" t="n"/>
+      <c r="N52" s="19" t="n"/>
+      <c r="O52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr"/>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>SDG 5 - Gender Equality</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F53" s="31" t="n"/>
+      <c r="G53" s="31" t="n"/>
+      <c r="H53" s="31" t="n"/>
+      <c r="I53" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="n"/>
+      <c r="L53" s="19" t="n"/>
+      <c r="M53" s="19" t="n"/>
+      <c r="N53" s="19" t="n"/>
+      <c r="O53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr"/>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>SDG 6 - Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="n"/>
+      <c r="G54" s="31" t="n"/>
+      <c r="H54" s="31" t="n"/>
+      <c r="I54" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="n"/>
+      <c r="L54" s="19" t="n"/>
+      <c r="M54" s="19" t="n"/>
+      <c r="N54" s="19" t="n"/>
+      <c r="O54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr"/>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>SDG 7 - Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F55" s="31" t="n"/>
+      <c r="G55" s="31" t="n"/>
+      <c r="H55" s="31" t="n"/>
+      <c r="I55" s="31" t="n">
+        <v>34</v>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="n"/>
+      <c r="L55" s="19" t="n"/>
+      <c r="M55" s="19" t="n"/>
+      <c r="N55" s="19" t="n"/>
+      <c r="O55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr"/>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>SDG 8 - Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F56" s="31" t="n"/>
+      <c r="G56" s="31" t="n"/>
+      <c r="H56" s="31" t="n"/>
+      <c r="I56" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K56" s="19" t="n"/>
+      <c r="L56" s="19" t="n"/>
+      <c r="M56" s="19" t="n"/>
+      <c r="N56" s="19" t="n"/>
+      <c r="O56" s="19" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr"/>
+      <c r="D57" s="30" t="inlineStr">
+        <is>
+          <t>SDG 9 - Industry, innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F57" s="31" t="n"/>
+      <c r="G57" s="31" t="n"/>
+      <c r="H57" s="31" t="n"/>
+      <c r="I57" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="n"/>
+      <c r="L57" s="19" t="n"/>
+      <c r="M57" s="19" t="n"/>
+      <c r="N57" s="19" t="n"/>
+      <c r="O57" s="19" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr"/>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>SDG 10 - Reduced inequality</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F58" s="31" t="n"/>
+      <c r="G58" s="31" t="n"/>
+      <c r="H58" s="31" t="n"/>
+      <c r="I58" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K58" s="19" t="n"/>
+      <c r="L58" s="19" t="n"/>
+      <c r="M58" s="19" t="n"/>
+      <c r="N58" s="19" t="n"/>
+      <c r="O58" s="19" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr"/>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>SDG 11 - Sustainable cities and communities</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F59" s="31" t="n"/>
+      <c r="G59" s="31" t="n"/>
+      <c r="H59" s="31" t="n"/>
+      <c r="I59" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="n"/>
+      <c r="L59" s="19" t="n"/>
+      <c r="M59" s="19" t="n"/>
+      <c r="N59" s="19" t="n"/>
+      <c r="O59" s="19" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr"/>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>SDG 12 - Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F60" s="31" t="n"/>
+      <c r="G60" s="31" t="n"/>
+      <c r="H60" s="31" t="n"/>
+      <c r="I60" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="n"/>
+      <c r="L60" s="19" t="n"/>
+      <c r="M60" s="19" t="n"/>
+      <c r="N60" s="19" t="n"/>
+      <c r="O60" s="19" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr"/>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>SDG 13 - Climate action</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F61" s="31" t="n"/>
+      <c r="G61" s="31" t="n"/>
+      <c r="H61" s="31" t="n"/>
+      <c r="I61" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="n"/>
+      <c r="L61" s="19" t="n"/>
+      <c r="M61" s="19" t="n"/>
+      <c r="N61" s="19" t="n"/>
+      <c r="O61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr"/>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>SDG 14 - Life below water</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F62" s="31" t="n"/>
+      <c r="G62" s="31" t="n"/>
+      <c r="H62" s="31" t="n"/>
+      <c r="I62" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K62" s="19" t="n"/>
+      <c r="L62" s="19" t="n"/>
+      <c r="M62" s="19" t="n"/>
+      <c r="N62" s="19" t="n"/>
+      <c r="O62" s="19" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr"/>
+      <c r="D63" s="30" t="inlineStr">
+        <is>
+          <t>SDG 15 - Life on land</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F63" s="31" t="n"/>
+      <c r="G63" s="31" t="n"/>
+      <c r="H63" s="31" t="n"/>
+      <c r="I63" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="n"/>
+      <c r="L63" s="19" t="n"/>
+      <c r="M63" s="19" t="n"/>
+      <c r="N63" s="19" t="n"/>
+      <c r="O63" s="19" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr"/>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>SDG 16 - Peace, justice and strong institutions</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F64" s="31" t="n"/>
+      <c r="G64" s="31" t="n"/>
+      <c r="H64" s="31" t="n"/>
+      <c r="I64" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="n"/>
+      <c r="L64" s="19" t="n"/>
+      <c r="M64" s="19" t="n"/>
+      <c r="N64" s="19" t="n"/>
+      <c r="O64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr"/>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>SDG 17 - Partnerships</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F65" s="31" t="n"/>
+      <c r="G65" s="31" t="n"/>
+      <c r="H65" s="31" t="n"/>
+      <c r="I65" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="n"/>
+      <c r="L65" s="19" t="n"/>
+      <c r="M65" s="19" t="n"/>
+      <c r="N65" s="19" t="n"/>
+      <c r="O65" s="19" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr"/>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>SDG-related research outputs mentioned in Policy and related documents</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F66" s="31" t="n"/>
+      <c r="G66" s="31" t="n"/>
+      <c r="H66" s="31" t="n"/>
+      <c r="I66" s="31" t="n">
+        <v>1256</v>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="n"/>
+      <c r="L66" s="19" t="n"/>
+      <c r="M66" s="19" t="n"/>
+      <c r="N66" s="19" t="n"/>
+      <c r="O66" s="19" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr"/>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>SDG 1 - No Poverty</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F67" s="31" t="n"/>
+      <c r="G67" s="31" t="n"/>
+      <c r="H67" s="31" t="n"/>
+      <c r="I67" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="n"/>
+      <c r="L67" s="19" t="n"/>
+      <c r="M67" s="19" t="n"/>
+      <c r="N67" s="19" t="n"/>
+      <c r="O67" s="19" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr"/>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>SDG 2 - Zero Hunger</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="n"/>
+      <c r="G68" s="31" t="n"/>
+      <c r="H68" s="31" t="n"/>
+      <c r="I68" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K68" s="19" t="n"/>
+      <c r="L68" s="19" t="n"/>
+      <c r="M68" s="19" t="n"/>
+      <c r="N68" s="19" t="n"/>
+      <c r="O68" s="19" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr"/>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>SDG 3 - Good health and well-being</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="n"/>
+      <c r="G69" s="31" t="n"/>
+      <c r="H69" s="31" t="n"/>
+      <c r="I69" s="31" t="n">
+        <v>676</v>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="n"/>
+      <c r="L69" s="19" t="n"/>
+      <c r="M69" s="19" t="n"/>
+      <c r="N69" s="19" t="n"/>
+      <c r="O69" s="19" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr"/>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>SDG 4 - Quality Education</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="n"/>
+      <c r="G70" s="31" t="n"/>
+      <c r="H70" s="31" t="n"/>
+      <c r="I70" s="31" t="n">
+        <v>48</v>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K70" s="19" t="n"/>
+      <c r="L70" s="19" t="n"/>
+      <c r="M70" s="19" t="n"/>
+      <c r="N70" s="19" t="n"/>
+      <c r="O70" s="19" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr"/>
+      <c r="D71" s="30" t="inlineStr">
+        <is>
+          <t>SDG 5 - Gender Equality</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="n"/>
+      <c r="G71" s="31" t="n"/>
+      <c r="H71" s="31" t="n"/>
+      <c r="I71" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="n"/>
+      <c r="L71" s="19" t="n"/>
+      <c r="M71" s="19" t="n"/>
+      <c r="N71" s="19" t="n"/>
+      <c r="O71" s="19" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr"/>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>SDG 6 - Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="n"/>
+      <c r="G72" s="31" t="n"/>
+      <c r="H72" s="31" t="n"/>
+      <c r="I72" s="31" t="n">
+        <v>32</v>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K72" s="19" t="n"/>
+      <c r="L72" s="19" t="n"/>
+      <c r="M72" s="19" t="n"/>
+      <c r="N72" s="19" t="n"/>
+      <c r="O72" s="19" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr"/>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>SDG 7 - Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="n"/>
+      <c r="G73" s="31" t="n"/>
+      <c r="H73" s="31" t="n"/>
+      <c r="I73" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="n"/>
+      <c r="L73" s="19" t="n"/>
+      <c r="M73" s="19" t="n"/>
+      <c r="N73" s="19" t="n"/>
+      <c r="O73" s="19" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr"/>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>SDG 8 - Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="n"/>
+      <c r="G74" s="31" t="n"/>
+      <c r="H74" s="31" t="n"/>
+      <c r="I74" s="31" t="n">
+        <v>31</v>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K74" s="19" t="n"/>
+      <c r="L74" s="19" t="n"/>
+      <c r="M74" s="19" t="n"/>
+      <c r="N74" s="19" t="n"/>
+      <c r="O74" s="19" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr"/>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>SDG 9 - Industry, innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="n"/>
+      <c r="G75" s="31" t="n"/>
+      <c r="H75" s="31" t="n"/>
+      <c r="I75" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K75" s="19" t="n"/>
+      <c r="L75" s="19" t="n"/>
+      <c r="M75" s="19" t="n"/>
+      <c r="N75" s="19" t="n"/>
+      <c r="O75" s="19" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr"/>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>SDG 10 - Reduced inequality</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="n"/>
+      <c r="G76" s="31" t="n"/>
+      <c r="H76" s="31" t="n"/>
+      <c r="I76" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K76" s="19" t="n"/>
+      <c r="L76" s="19" t="n"/>
+      <c r="M76" s="19" t="n"/>
+      <c r="N76" s="19" t="n"/>
+      <c r="O76" s="19" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr"/>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>SDG 11 - Sustainable cities and communities</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="n"/>
+      <c r="G77" s="31" t="n"/>
+      <c r="H77" s="31" t="n"/>
+      <c r="I77" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K77" s="19" t="n"/>
+      <c r="L77" s="19" t="n"/>
+      <c r="M77" s="19" t="n"/>
+      <c r="N77" s="19" t="n"/>
+      <c r="O77" s="19" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr"/>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>SDG 12 - Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="n"/>
+      <c r="G78" s="31" t="n"/>
+      <c r="H78" s="31" t="n"/>
+      <c r="I78" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K78" s="19" t="n"/>
+      <c r="L78" s="19" t="n"/>
+      <c r="M78" s="19" t="n"/>
+      <c r="N78" s="19" t="n"/>
+      <c r="O78" s="19" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr"/>
+      <c r="D79" s="30" t="inlineStr">
+        <is>
+          <t>SDG 13 - Climate action</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="n"/>
+      <c r="G79" s="31" t="n"/>
+      <c r="H79" s="31" t="n"/>
+      <c r="I79" s="31" t="n">
+        <v>193</v>
+      </c>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K79" s="19" t="n"/>
+      <c r="L79" s="19" t="n"/>
+      <c r="M79" s="19" t="n"/>
+      <c r="N79" s="19" t="n"/>
+      <c r="O79" s="19" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr"/>
+      <c r="D80" s="30" t="inlineStr">
+        <is>
+          <t>SDG 14 - Life below water</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="n"/>
+      <c r="G80" s="31" t="n"/>
+      <c r="H80" s="31" t="n"/>
+      <c r="I80" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K80" s="19" t="n"/>
+      <c r="L80" s="19" t="n"/>
+      <c r="M80" s="19" t="n"/>
+      <c r="N80" s="19" t="n"/>
+      <c r="O80" s="19" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr"/>
+      <c r="D81" s="30" t="inlineStr">
+        <is>
+          <t>SDG 15 - Life on land</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="n"/>
+      <c r="G81" s="31" t="n"/>
+      <c r="H81" s="31" t="n"/>
+      <c r="I81" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="n"/>
+      <c r="L81" s="19" t="n"/>
+      <c r="M81" s="19" t="n"/>
+      <c r="N81" s="19" t="n"/>
+      <c r="O81" s="19" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr"/>
+      <c r="D82" s="30" t="inlineStr">
+        <is>
+          <t>SDG 16 - Peace, justice and strong institutions</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="n"/>
+      <c r="G82" s="31" t="n"/>
+      <c r="H82" s="31" t="n"/>
+      <c r="I82" s="31" t="n">
+        <v>52</v>
+      </c>
+      <c r="J82" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K82" s="19" t="n"/>
+      <c r="L82" s="19" t="n"/>
+      <c r="M82" s="19" t="n"/>
+      <c r="N82" s="19" t="n"/>
+      <c r="O82" s="19" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr"/>
+      <c r="D83" s="30" t="inlineStr">
+        <is>
+          <t>SDG 17 - Partnerships</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="n"/>
+      <c r="G83" s="31" t="n"/>
+      <c r="H83" s="31" t="n"/>
+      <c r="I83" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="n"/>
+      <c r="L83" s="19" t="n"/>
+      <c r="M83" s="19" t="n"/>
+      <c r="N83" s="19" t="n"/>
+      <c r="O83" s="19" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr"/>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>SDG-related research outputs mentioned in News and Social Media</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="n"/>
+      <c r="G84" s="31" t="n"/>
+      <c r="H84" s="31" t="n"/>
+      <c r="I84" s="31" t="n">
+        <v>86993</v>
+      </c>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K84" s="19" t="n"/>
+      <c r="L84" s="19" t="n"/>
+      <c r="M84" s="19" t="n"/>
+      <c r="N84" s="19" t="n"/>
+      <c r="O84" s="19" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr"/>
+      <c r="D85" s="30" t="inlineStr">
+        <is>
+          <t>SDG 1 - No Poverty</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F85" s="31" t="n"/>
+      <c r="G85" s="31" t="n"/>
+      <c r="H85" s="31" t="n"/>
+      <c r="I85" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K85" s="19" t="n"/>
+      <c r="L85" s="19" t="n"/>
+      <c r="M85" s="19" t="n"/>
+      <c r="N85" s="19" t="n"/>
+      <c r="O85" s="19" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="inlineStr"/>
+      <c r="D86" s="30" t="inlineStr">
+        <is>
+          <t>SDG 2 - Zero Hunger</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F86" s="31" t="n"/>
+      <c r="G86" s="31" t="n"/>
+      <c r="H86" s="31" t="n"/>
+      <c r="I86" s="31" t="n">
+        <v>731</v>
+      </c>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K86" s="19" t="n"/>
+      <c r="L86" s="19" t="n"/>
+      <c r="M86" s="19" t="n"/>
+      <c r="N86" s="19" t="n"/>
+      <c r="O86" s="19" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr"/>
+      <c r="D87" s="30" t="inlineStr">
+        <is>
+          <t>SDG 3 - Good health and well-being</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F87" s="31" t="n"/>
+      <c r="G87" s="31" t="n"/>
+      <c r="H87" s="31" t="n"/>
+      <c r="I87" s="31" t="n">
+        <v>55989</v>
+      </c>
+      <c r="J87" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K87" s="19" t="n"/>
+      <c r="L87" s="19" t="n"/>
+      <c r="M87" s="19" t="n"/>
+      <c r="N87" s="19" t="n"/>
+      <c r="O87" s="19" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="inlineStr"/>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>SDG 4 - Quality Education</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F88" s="31" t="n"/>
+      <c r="G88" s="31" t="n"/>
+      <c r="H88" s="31" t="n"/>
+      <c r="I88" s="31" t="n">
+        <v>6263</v>
+      </c>
+      <c r="J88" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K88" s="19" t="n"/>
+      <c r="L88" s="19" t="n"/>
+      <c r="M88" s="19" t="n"/>
+      <c r="N88" s="19" t="n"/>
+      <c r="O88" s="19" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr"/>
+      <c r="D89" s="30" t="inlineStr">
+        <is>
+          <t>SDG 5 - Gender Equality</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F89" s="31" t="n"/>
+      <c r="G89" s="31" t="n"/>
+      <c r="H89" s="31" t="n"/>
+      <c r="I89" s="31" t="n">
+        <v>5286</v>
+      </c>
+      <c r="J89" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K89" s="19" t="n"/>
+      <c r="L89" s="19" t="n"/>
+      <c r="M89" s="19" t="n"/>
+      <c r="N89" s="19" t="n"/>
+      <c r="O89" s="19" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr"/>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>SDG 6 - Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F90" s="31" t="n"/>
+      <c r="G90" s="31" t="n"/>
+      <c r="H90" s="31" t="n"/>
+      <c r="I90" s="31" t="n">
+        <v>248</v>
+      </c>
+      <c r="J90" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K90" s="19" t="n"/>
+      <c r="L90" s="19" t="n"/>
+      <c r="M90" s="19" t="n"/>
+      <c r="N90" s="19" t="n"/>
+      <c r="O90" s="19" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr"/>
+      <c r="D91" s="30" t="inlineStr">
+        <is>
+          <t>SDG 7 - Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F91" s="31" t="n"/>
+      <c r="G91" s="31" t="n"/>
+      <c r="H91" s="31" t="n"/>
+      <c r="I91" s="31" t="n">
+        <v>1009</v>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K91" s="19" t="n"/>
+      <c r="L91" s="19" t="n"/>
+      <c r="M91" s="19" t="n"/>
+      <c r="N91" s="19" t="n"/>
+      <c r="O91" s="19" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr"/>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>SDG 8 - Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F92" s="31" t="n"/>
+      <c r="G92" s="31" t="n"/>
+      <c r="H92" s="31" t="n"/>
+      <c r="I92" s="31" t="n">
+        <v>844</v>
+      </c>
+      <c r="J92" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K92" s="19" t="n"/>
+      <c r="L92" s="19" t="n"/>
+      <c r="M92" s="19" t="n"/>
+      <c r="N92" s="19" t="n"/>
+      <c r="O92" s="19" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr"/>
+      <c r="D93" s="30" t="inlineStr">
+        <is>
+          <t>SDG 9 - Industry, innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F93" s="31" t="n"/>
+      <c r="G93" s="31" t="n"/>
+      <c r="H93" s="31" t="n"/>
+      <c r="I93" s="31" t="n">
+        <v>48</v>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K93" s="19" t="n"/>
+      <c r="L93" s="19" t="n"/>
+      <c r="M93" s="19" t="n"/>
+      <c r="N93" s="19" t="n"/>
+      <c r="O93" s="19" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr"/>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>SDG 10 - Reduced inequality</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F94" s="31" t="n"/>
+      <c r="G94" s="31" t="n"/>
+      <c r="H94" s="31" t="n"/>
+      <c r="I94" s="31" t="n">
+        <v>1032</v>
+      </c>
+      <c r="J94" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K94" s="19" t="n"/>
+      <c r="L94" s="19" t="n"/>
+      <c r="M94" s="19" t="n"/>
+      <c r="N94" s="19" t="n"/>
+      <c r="O94" s="19" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr"/>
+      <c r="D95" s="30" t="inlineStr">
+        <is>
+          <t>SDG 11 - Sustainable cities and communities</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F95" s="31" t="n"/>
+      <c r="G95" s="31" t="n"/>
+      <c r="H95" s="31" t="n"/>
+      <c r="I95" s="31" t="n">
+        <v>400</v>
+      </c>
+      <c r="J95" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="n"/>
+      <c r="L95" s="19" t="n"/>
+      <c r="M95" s="19" t="n"/>
+      <c r="N95" s="19" t="n"/>
+      <c r="O95" s="19" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr"/>
+      <c r="D96" s="30" t="inlineStr">
+        <is>
+          <t>SDG 12 - Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F96" s="31" t="n"/>
+      <c r="G96" s="31" t="n"/>
+      <c r="H96" s="31" t="n"/>
+      <c r="I96" s="31" t="n">
+        <v>224</v>
+      </c>
+      <c r="J96" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K96" s="19" t="n"/>
+      <c r="L96" s="19" t="n"/>
+      <c r="M96" s="19" t="n"/>
+      <c r="N96" s="19" t="n"/>
+      <c r="O96" s="19" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr"/>
+      <c r="D97" s="30" t="inlineStr">
+        <is>
+          <t>SDG 13 - Climate action</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F97" s="31" t="n"/>
+      <c r="G97" s="31" t="n"/>
+      <c r="H97" s="31" t="n"/>
+      <c r="I97" s="31" t="n">
+        <v>9639</v>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="n"/>
+      <c r="L97" s="19" t="n"/>
+      <c r="M97" s="19" t="n"/>
+      <c r="N97" s="19" t="n"/>
+      <c r="O97" s="19" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr"/>
+      <c r="D98" s="30" t="inlineStr">
+        <is>
+          <t>SDG 14 - Life below water</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F98" s="31" t="n"/>
+      <c r="G98" s="31" t="n"/>
+      <c r="H98" s="31" t="n"/>
+      <c r="I98" s="31" t="n">
+        <v>1503</v>
+      </c>
+      <c r="J98" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K98" s="19" t="n"/>
+      <c r="L98" s="19" t="n"/>
+      <c r="M98" s="19" t="n"/>
+      <c r="N98" s="19" t="n"/>
+      <c r="O98" s="19" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr"/>
+      <c r="D99" s="30" t="inlineStr">
+        <is>
+          <t>SDG 15 - Life on land</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F99" s="31" t="n"/>
+      <c r="G99" s="31" t="n"/>
+      <c r="H99" s="31" t="n"/>
+      <c r="I99" s="31" t="n">
+        <v>2844</v>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="n"/>
+      <c r="L99" s="19" t="n"/>
+      <c r="M99" s="19" t="n"/>
+      <c r="N99" s="19" t="n"/>
+      <c r="O99" s="19" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr"/>
+      <c r="D100" s="30" t="inlineStr">
+        <is>
+          <t>SDG 16 - Peace, justice and strong institutions</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F100" s="31" t="n"/>
+      <c r="G100" s="31" t="n"/>
+      <c r="H100" s="31" t="n"/>
+      <c r="I100" s="31" t="n">
+        <v>916</v>
+      </c>
+      <c r="J100" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K100" s="19" t="n"/>
+      <c r="L100" s="19" t="n"/>
+      <c r="M100" s="19" t="n"/>
+      <c r="N100" s="19" t="n"/>
+      <c r="O100" s="19" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>TR2(c)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr"/>
+      <c r="D101" s="30" t="inlineStr">
+        <is>
+          <t>SDG 17 - Partnerships</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F101" s="31" t="n"/>
+      <c r="G101" s="31" t="n"/>
+      <c r="H101" s="31" t="n"/>
+      <c r="I101" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t>Data held</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="n"/>
+      <c r="L101" s="19" t="n"/>
+      <c r="M101" s="19" t="n"/>
+      <c r="N101" s="19" t="n"/>
+      <c r="O101" s="19" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>TR3(b)</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>Laboratories achieveng Green Lab Ceritifcation</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F102" s="31" t="n"/>
+      <c r="G102" s="31" t="n"/>
+      <c r="H102" s="31" t="n"/>
+      <c r="I102" s="31" t="n"/>
+      <c r="J102" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K102" s="19" t="n"/>
+      <c r="L102" s="19" t="n"/>
+      <c r="M102" s="19" t="n"/>
+      <c r="N102" s="19" t="n"/>
+      <c r="O102" s="19" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>TR3(b)</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr"/>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>New Sustainable Activities</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F103" s="31" t="n"/>
+      <c r="G103" s="31" t="n"/>
+      <c r="H103" s="31" t="n"/>
+      <c r="I103" s="31" t="n"/>
+      <c r="J103" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K103" s="19" t="n"/>
+      <c r="L103" s="19" t="n"/>
+      <c r="M103" s="19" t="n"/>
+      <c r="N103" s="19" t="n"/>
+      <c r="O103" s="19" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>TR3(b)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr"/>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>Sustainable Fieldworks</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F104" s="31" t="n"/>
+      <c r="G104" s="31" t="n"/>
+      <c r="H104" s="31" t="n"/>
+      <c r="I104" s="31" t="n"/>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K104" s="19" t="n"/>
+      <c r="L104" s="19" t="n"/>
+      <c r="M104" s="19" t="n"/>
+      <c r="N104" s="19" t="n"/>
+      <c r="O104" s="19" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t>Documented baseline nature footprint analysis</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>Freshwater eutrophication</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>kg P eq</t>
+        </is>
+      </c>
+      <c r="F105" s="31" t="n"/>
+      <c r="G105" s="31" t="n"/>
+      <c r="H105" s="31" t="n"/>
+      <c r="I105" s="31" t="n"/>
+      <c r="J105" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K105" s="19" t="n"/>
+      <c r="L105" s="19" t="n"/>
+      <c r="M105" s="19" t="n"/>
+      <c r="N105" s="19" t="n"/>
+      <c r="O105" s="19" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="inlineStr"/>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>Global warming</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>kg CO2 eq</t>
+        </is>
+      </c>
+      <c r="F106" s="31" t="n"/>
+      <c r="G106" s="31" t="n"/>
+      <c r="H106" s="31" t="n"/>
+      <c r="I106" s="31" t="n"/>
+      <c r="J106" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K106" s="19" t="n"/>
+      <c r="L106" s="19" t="n"/>
+      <c r="M106" s="19" t="n"/>
+      <c r="N106" s="19" t="n"/>
+      <c r="O106" s="19" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="inlineStr"/>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>Land use</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>m²a crop eq</t>
+        </is>
+      </c>
+      <c r="F107" s="31" t="n"/>
+      <c r="G107" s="31" t="n"/>
+      <c r="H107" s="31" t="n"/>
+      <c r="I107" s="31" t="n"/>
+      <c r="J107" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K107" s="19" t="n"/>
+      <c r="L107" s="19" t="n"/>
+      <c r="M107" s="19" t="n"/>
+      <c r="N107" s="19" t="n"/>
+      <c r="O107" s="19" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr"/>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>Marine eutrophication</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>kg N eq</t>
+        </is>
+      </c>
+      <c r="F108" s="31" t="n"/>
+      <c r="G108" s="31" t="n"/>
+      <c r="H108" s="31" t="n"/>
+      <c r="I108" s="31" t="n"/>
+      <c r="J108" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K108" s="19" t="n"/>
+      <c r="L108" s="19" t="n"/>
+      <c r="M108" s="19" t="n"/>
+      <c r="N108" s="19" t="n"/>
+      <c r="O108" s="19" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr"/>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>Photochemical ozone formation</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>kg NOx eq</t>
+        </is>
+      </c>
+      <c r="F109" s="31" t="n"/>
+      <c r="G109" s="31" t="n"/>
+      <c r="H109" s="31" t="n"/>
+      <c r="I109" s="31" t="n"/>
+      <c r="J109" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K109" s="19" t="n"/>
+      <c r="L109" s="19" t="n"/>
+      <c r="M109" s="19" t="n"/>
+      <c r="N109" s="19" t="n"/>
+      <c r="O109" s="19" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr"/>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>Terrestrial acidification</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="F110" s="31" t="n"/>
+      <c r="G110" s="31" t="n"/>
+      <c r="H110" s="31" t="n"/>
+      <c r="I110" s="31" t="n"/>
+      <c r="J110" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K110" s="19" t="n"/>
+      <c r="L110" s="19" t="n"/>
+      <c r="M110" s="19" t="n"/>
+      <c r="N110" s="19" t="n"/>
+      <c r="O110" s="19" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>NB2(a)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr"/>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>Water consumption</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F111" s="31" t="n"/>
+      <c r="G111" s="31" t="n"/>
+      <c r="H111" s="31" t="n"/>
+      <c r="I111" s="31" t="n"/>
+      <c r="J111" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K111" s="19" t="n"/>
+      <c r="L111" s="19" t="n"/>
+      <c r="M111" s="19" t="n"/>
+      <c r="N111" s="19" t="n"/>
+      <c r="O111" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="K5:O5"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="M8:M112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+      <formula1>"No change,Yes – see notes"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>End 2026 target status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data owner confirms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Request status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Please select from dropdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially – see comments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chased</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support meeting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>